--- a/relatorio_financeiro.xlsx
+++ b/relatorio_financeiro.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo Geral" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalhes dos Lançamentos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo Mensal" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,12 +427,70 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Saldo Inicial (R$)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Saldo Final (R$)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Variação Percentual (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total de Entradas (+R$)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total de Saídas (-R$)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1531</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1570.01</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.548007838014369</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3500.99</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2009.99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>Código</t>
         </is>
       </c>
@@ -466,24 +526,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01/02/2025</t>
+          <t>28/01/2025</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>entrada</t>
+          <t>saida</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Um</t>
+          <t>carne</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="3">
@@ -492,24 +552,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>02/02/2025</t>
+          <t>28/01/2025</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>entrada</t>
+          <t>saida</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dois</t>
+          <t>cebola</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="4">
@@ -518,11 +578,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>03/02/2025</t>
+          <t>28/01/2025</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -531,11 +591,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Três</t>
+          <t>tomate</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="5">
@@ -544,24 +604,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>04/02/2025</t>
+          <t>28/01/2025</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>entrada</t>
+          <t>saida</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Quatro</t>
+          <t>arroz</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="6">
@@ -570,11 +630,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>01/02/2025</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -583,11 +643,209 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>cinco</t>
+          <t>salario</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>01/02/2025</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>saida</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>café</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3486</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>01/02/2025</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>saida</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>pão</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3478</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>01/02/2025</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>saida</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>leite</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3470</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>07/02/2025</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>bombom</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01/02/2025</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>saida</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>carro</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1570.01</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mes_Ano</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>saida</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Saldo Mensal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3500.99</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1929.99</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1571</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_financeiro.xlsx
+++ b/relatorio_financeiro.xlsx
@@ -459,19 +459,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1531</v>
+        <v>5560</v>
       </c>
       <c r="B2" t="n">
-        <v>1570.01</v>
+        <v>5600</v>
       </c>
       <c r="C2" t="n">
-        <v>2.548007838014369</v>
+        <v>0.7194244604316548</v>
       </c>
       <c r="D2" t="n">
-        <v>3500.99</v>
+        <v>7600.99</v>
       </c>
       <c r="E2" t="n">
-        <v>2009.99</v>
+        <v>2080.99</v>
       </c>
     </row>
   </sheetData>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1531</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="3">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1527</v>
+        <v>5556</v>
       </c>
     </row>
     <row r="4">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1521</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="5">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1491</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="6">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3500</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="7">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3486</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="8">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3478</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="9">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3470</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="10">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1571</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="11">
@@ -777,7 +777,189 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1570.01</v>
+        <v>1610.01</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>40</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>carne</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>22/01/2025</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>saida</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>carne</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>5570</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>02/01/2025</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>23</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>saida</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>galinha</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1587.01</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>16/02/2025</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>saida</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>pão</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>5610</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>15/01/2025</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>carne</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>5618</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>04/03/2025</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>arroz</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1617.01</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>24/12/2024</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>arroz</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>5600</v>
       </c>
     </row>
   </sheetData>
@@ -791,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,33 +1001,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="n">
-        <v>80</v>
-      </c>
       <c r="D2" t="n">
-        <v>-80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4040</v>
+      </c>
+      <c r="C3" t="n">
+        <v>143</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>2025-02</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
         <v>3500.99</v>
       </c>
-      <c r="C3" t="n">
-        <v>1929.99</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1571</v>
+      <c r="C4" t="n">
+        <v>1937.99</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
